--- a/results/Int All Data -0.7/Rando_6_permute.xlsx
+++ b/results/Int All Data -0.7/Rando_6_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8880139036323439</v>
+        <v>0.8905218650980518</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8882924551643774</v>
+        <v>0.9008288703897327</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8885710066964108</v>
+        <v>0.9005900264184977</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8897251199208243</v>
+        <v>0.9017441396429113</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8853475109944051</v>
+        <v>0.9051266651235923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8829995769847794</v>
+        <v>0.9038135221205035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8834373578309695</v>
+        <v>0.9052461868769505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8823628592636343</v>
+        <v>0.9032562195209553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8864220095617403</v>
+        <v>0.8997142651906362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8868597904079303</v>
+        <v>0.8851487736549313</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8868597904079303</v>
+        <v>0.8954956860428922</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8874965081290755</v>
+        <v>0.8969283507993391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.886780175750852</v>
+        <v>0.8966497992673057</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8838352315808797</v>
+        <v>0.8946600314467918</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8841137831129131</v>
+        <v>0.8957345300141271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8843923346449465</v>
+        <v>0.8957345300141271</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.873288983247001</v>
+        <v>0.8828806538378655</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8762339274169733</v>
+        <v>0.8842335044017526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8762339274169733</v>
+        <v>0.8600769408816276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8762339274169733</v>
+        <v>0.8464666256953812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8697073213558835</v>
+        <v>0.8451532831568109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8608327812851682</v>
+        <v>0.8402981858234031</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8640562769871738</v>
+        <v>0.8368757532464423</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8647726093653973</v>
+        <v>0.836557294618129</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8658471079327326</v>
+        <v>0.8365972017144088</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8664042109967994</v>
+        <v>0.8260511529160115</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8577286078010391</v>
+        <v>0.8182511114126314</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8586041694934193</v>
+        <v>0.8182511114126314</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8599175120319895</v>
+        <v>0.8096551228739495</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8508440350863191</v>
+        <v>0.7984721568189255</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8519185336536543</v>
+        <v>0.7971191067195569</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8433622526757707</v>
+        <v>0.8133561069829438</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8338114868585932</v>
+        <v>0.8083022723100621</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8354430884899953</v>
+        <v>0.8049195472938998</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.833413613108683</v>
+        <v>0.8025317061879944</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8337717792977948</v>
+        <v>0.8278820904933315</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7852601144535521</v>
+        <v>0.8278820904933315</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7878468924344126</v>
+        <v>0.8306280977883487</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.786493842335044</v>
+        <v>0.8279617051504098</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7838274496971052</v>
+        <v>0.8317025963556839</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7838274496971052</v>
+        <v>0.8325382509517842</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.785578373546384</v>
+        <v>0.8360402981858235</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7822752631873</v>
+        <v>0.83576174665379</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7796884852064394</v>
+        <v>0.8352046435897231</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.773002649831193</v>
+        <v>0.8511231852247967</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7632130400427803</v>
+        <v>0.833294689961769</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7632130400427803</v>
+        <v>0.836836644292088</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.729107637420086</v>
+        <v>0.8314647500618559</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7354750141670192</v>
+        <v>0.8277240583920633</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7316148007438683</v>
+        <v>0.8223912731161855</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7330474655003153</v>
+        <v>0.8246994995650127</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7367486491447909</v>
+        <v>0.8198841097924032</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7650836851808989</v>
+        <v>0.8165807998978378</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7616213455076581</v>
+        <v>0.8159043746158943</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7503988714273172</v>
+        <v>0.8159043746158943</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7556917496069151</v>
+        <v>0.8062739941416383</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7631338244566649</v>
+        <v>0.7985535672953364</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7704563775530564</v>
+        <v>0.7917883167984932</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7685859319504194</v>
+        <v>0.7891221236960357</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7697001380785531</v>
+        <v>0.7887639575069239</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7525079614657078</v>
+        <v>0.7582412144527539</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7484885187284003</v>
+        <v>0.7539829277442115</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7542191777541882</v>
+        <v>0.7605095338053013</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7689440981395312</v>
+        <v>0.7660813625878954</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7657605095338054</v>
+        <v>0.7493271663567216</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7544981283571844</v>
+        <v>0.7255686761219879</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7447484256650518</v>
+        <v>0.7202757979423902</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7447484256650518</v>
+        <v>0.7303042517020377</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7447484256650518</v>
+        <v>0.7296276268846127</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7410871491168559</v>
+        <v>0.7310203845447798</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7404109233703937</v>
+        <v>0.7187625208514579</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7376653151463393</v>
+        <v>0.7082176692659489</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7369489827681158</v>
+        <v>0.6661911071026649</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7318554405344357</v>
+        <v>0.6450589028741091</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7220656312105419</v>
+        <v>0.6450589028741091</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7219064018963852</v>
+        <v>0.6519825845431835</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7219064018963852</v>
+        <v>0.6433865960045015</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7193992385726029</v>
+        <v>0.6612951049955703</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7064655482037816</v>
+        <v>0.6663890463002131</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6985457854115619</v>
+        <v>0.6577930577615312</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6858100342402886</v>
+        <v>0.6577930577615312</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6789649695508855</v>
+        <v>0.6641622303277969</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6800392685827394</v>
+        <v>0.6535357687303956</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6668270266818845</v>
+        <v>0.6394080580408809</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6610167529990183</v>
+        <v>0.6419948360217413</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6149719453113153</v>
+        <v>0.6378179597896098</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5826573736341796</v>
+        <v>0.6098799993614864</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5830155398232914</v>
+        <v>0.6181966382262094</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5847267561117718</v>
+        <v>0.619589595421858</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5847267561117718</v>
+        <v>0.568371830378878</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5814236457526878</v>
+        <v>0.5516569426375398</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.597540924727235</v>
+        <v>0.5668988594551884</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.597540924727235</v>
+        <v>0.5208147432776496</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5981778419838616</v>
+        <v>0.4952255150010775</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6033112913138214</v>
+        <v>0.4963000135684127</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.616881699403788</v>
+        <v>0.4963000135684127</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6133000375126705</v>
+        <v>0.495941847379301</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6188317596635033</v>
+        <v>0.495941847379301</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6111909474742798</v>
+        <v>0.4957826180651443</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.603231676656743</v>
+        <v>0.4992445586674222</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5710763342937641</v>
+        <v>0.4970159468756735</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5649875090788644</v>
+        <v>0.498846684917512</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5650671237359427</v>
+        <v>0.4918830961521578</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5582220590465397</v>
+        <v>0.4886196933538722</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.56041096327749</v>
+        <v>0.4901718798636774</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5600527970883782</v>
+        <v>0.4929176876232131</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.574897039691598</v>
+        <v>0.4930370098410899</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5745388735024862</v>
+        <v>0.4927586578445379</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5538446496556018</v>
+        <v>0.4935941129051568</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.552053818710043</v>
+        <v>0.4955838807256706</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5376872640492932</v>
+        <v>0.4889784581494281</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5388413772737068</v>
+        <v>0.4867498463576793</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.53828427420964</v>
+        <v>0.4841632679123001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5386424403987518</v>
+        <v>0.484720370976367</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5496659776041375</v>
+        <v>0.4453649903025756</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5265044975297507</v>
+        <v>0.4465588110877876</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5321555418984604</v>
+        <v>0.435695301338484</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5321555418984604</v>
+        <v>0.4409875809116377</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5195004030616724</v>
+        <v>0.4470360999592947</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5129737970005827</v>
+        <v>0.4827304036203718</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5083176365421299</v>
+        <v>0.4813374464247233</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5083176365421299</v>
+        <v>0.4842420844274529</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5076410117247049</v>
+        <v>0.4925986303884557</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5076410117247049</v>
+        <v>0.4921608495422656</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5170335459051328</v>
+        <v>0.4873061512798206</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5198192607609485</v>
+        <v>0.4873061512798206</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5204162709212952</v>
+        <v>0.4873061512798206</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5217294139243841</v>
+        <v>0.48519706124143</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5179089080620316</v>
+        <v>0.4878233472476076</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5170732534659314</v>
+        <v>0.4958217270194986</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5146864100374329</v>
+        <v>0.4953442386125101</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4815387777254552</v>
+        <v>0.4953442386125101</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4795891165367026</v>
+        <v>0.4953442386125101</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4729834944249787</v>
+        <v>0.4953442386125101</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4750935821407763</v>
+        <v>0.4993235747180564</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4685290643382206</v>
+        <v>0.499045023186023</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4571485581566114</v>
+        <v>0.4923597864172207</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4594958935597928</v>
+        <v>0.495901341676577</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4808633501209185</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4674521713451086</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4647462706818526</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4933580624306614</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.497934209161073</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5111845623388751</v>
+        <v>0.5000796146570783</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5028280163778723</v>
+        <v>0.4996021262500898</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5041413589164425</v>
+        <v>0.5007961465707832</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5014749662785036</v>
+        <v>0.5007961465707832</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.479907176094053</v>
+        <v>0.4990849302823028</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4817772226257273</v>
+        <v>0.4946678133305665</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4823740332505926</v>
+        <v>0.4946678133305665</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4823740332505926</v>
+        <v>0.492678245045534</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.495782418529663</v>
+        <v>0.4935536072024327</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4993636813498176</v>
+        <v>0.4935536072024327</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4994830035676944</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4994830035676944</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
